--- a/tests/single_cif_file_test/539016/output/539016_pairs.xlsx
+++ b/tests/single_cif_file_test/539016/output/539016_pairs.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ga" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.291</v>
+        <v>2.358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.358</v>
+        <v>2.601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.601</v>
+        <v>3.291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
